--- a/data/trans_dic/IQ2605_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ2605_R2-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78,59%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>75,7%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>85,48%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>75,15%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>78,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,74%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,04; 82,55</t>
+          <t>71,65; 84,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,35; 89,81</t>
+          <t>85,24; 94,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,93; 80,9</t>
+          <t>74,47; 86,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,72; 100,0</t>
+          <t>70,85; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,88; 85,02</t>
+          <t>67,53; 82,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,68; 94,14</t>
+          <t>79,62; 90,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,66; 86,18</t>
+          <t>68,85; 80,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,1; 100,0</t>
+          <t>78,92; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,28; 82,1</t>
+          <t>72,04; 81,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83,71; 90,9</t>
+          <t>83,83; 90,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73,56; 82,17</t>
+          <t>73,22; 81,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,68; 97,18</t>
+          <t>81,7; 97,97</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84,26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>59,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>76,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>84,22%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>85,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,28; 64,16</t>
+          <t>48,11; 57,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,61; 80,66</t>
+          <t>73,4; 82,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,49; 87,87</t>
+          <t>79,78; 87,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,42; 92,54</t>
+          <t>76,12; 94,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,5; 58,06</t>
+          <t>54,27; 64,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,49; 81,67</t>
+          <t>71,9; 81,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,35; 87,84</t>
+          <t>79,73; 87,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,41; 93,87</t>
+          <t>75,19; 92,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,63; 59,7</t>
+          <t>52,21; 59,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,67; 80,25</t>
+          <t>73,96; 80,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,18; 86,86</t>
+          <t>81,22; 86,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,21; 91,3</t>
+          <t>79,04; 91,56</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>63,58%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70,5%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>47,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>74,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>75,21%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,11; 53,97</t>
+          <t>43,39; 57,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,08; 79,6</t>
+          <t>57,1; 70,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,07; 80,48</t>
+          <t>73,08; 83,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58,45; 84,44</t>
+          <t>58,1; 81,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,59; 57,82</t>
+          <t>39,89; 54,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,24; 70,11</t>
+          <t>67,25; 79,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,95; 82,83</t>
+          <t>69,32; 79,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,85; 79,4</t>
+          <t>57,0; 81,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,77; 53,7</t>
+          <t>43,53; 53,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,29; 73,18</t>
+          <t>64,59; 73,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,01; 80,42</t>
+          <t>72,9; 80,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,78; 78,49</t>
+          <t>62,33; 79,56</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>72,67%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>41,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>60,17%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>67,49%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,62%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,77; 46,77</t>
+          <t>36,34; 46,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,77; 65,94</t>
+          <t>57,59; 70,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,17; 73,08</t>
+          <t>65,69; 76,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,77; 69,33</t>
+          <t>61,11; 80,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,87; 46,78</t>
+          <t>35,84; 47,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,15; 69,31</t>
+          <t>53,46; 66,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,97; 77,29</t>
+          <t>60,96; 73,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,57; 81,34</t>
+          <t>47,17; 69,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,24; 45,06</t>
+          <t>37,65; 45,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,88; 66,07</t>
+          <t>57,83; 65,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65,44; 73,55</t>
+          <t>65,19; 73,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,93; 74,14</t>
+          <t>58,68; 74,1</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,7; 56,96</t>
+          <t>49,8; 55,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,62</t>
+          <t>70,59; 75,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,37; 78,56</t>
+          <t>76,43; 81,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,58; 77,76</t>
+          <t>70,69; 81,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>49,62; 55,78</t>
+          <t>51,06; 57,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,52; 75,94</t>
+          <t>70,61; 76,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,32; 81,49</t>
+          <t>73,26; 78,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>70,27; 82,03</t>
+          <t>64,42; 77,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,23; 55,57</t>
+          <t>51,22; 55,46</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71,3; 75,34</t>
+          <t>71,27; 75,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75,76; 79,45</t>
+          <t>75,71; 79,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>70,5; 78,57</t>
+          <t>69,65; 78,26</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83260</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>106340</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>94185</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>68325</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>107029</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>90794</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12873</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>83260</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>106340</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94185</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>22116</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61410; 74514</t>
+          <t>75909; 89592</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99348; 112446</t>
+          <t>100524; 111246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82069; 97745</t>
+          <t>86864; 100545</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10825; 13752</t>
+          <t>7912; 11166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76158; 90073</t>
+          <t>60951; 74454</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99861; 111021</t>
+          <t>99697; 113063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87093; 100528</t>
+          <t>83184; 97362</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8743; 14310</t>
+          <t>10045; 12729</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141821; 161082</t>
+          <t>141356; 160276</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203529; 221017</t>
+          <t>203826; 221121</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174692; 195129</t>
+          <t>173885; 194012</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21517; 27271</t>
+          <t>19522; 23411</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>134273</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>208930</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>217452</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>34378</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>149920</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>180874</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>177289</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29222</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>134273</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>208930</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>217452</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39084</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68307</t>
+          <t>60438</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>137202; 162160</t>
+          <t>122091; 146547</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>169174; 190555</t>
+          <t>196929; 220174</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167332; 184977</t>
+          <t>205872; 226375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25212; 31779</t>
+          <t>30051; 37353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>120540; 147327</t>
+          <t>137159; 162268</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>197171; 219125</t>
+          <t>169859; 191444</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>207345; 226677</t>
+          <t>167855; 185213</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35099; 42020</t>
+          <t>23006; 28177</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>266556; 302371</t>
+          <t>264433; 300317</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>371709; 404892</t>
+          <t>373185; 404952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380376; 406989</t>
+          <t>380589; 406900</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62655; 72225</t>
+          <t>55392; 64160</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>165</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>100824</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147479</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37570</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>60152</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>115769</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>141693</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28710</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>71332</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100824</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>147479</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>65019</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51165; 68843</t>
+          <t>61407; 81171</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>106088; 124049</t>
+          <t>90542; 111204</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132019; 151634</t>
+          <t>137815; 156971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23385; 33783</t>
+          <t>30965; 43512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61692; 81824</t>
+          <t>50881; 69060</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90768; 111171</t>
+          <t>104805; 124370</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>137570; 156187</t>
+          <t>130608; 149995</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31789; 44397</t>
+          <t>21920; 31525</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117757; 144474</t>
+          <t>117122; 143986</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>202119; 230091</t>
+          <t>203069; 231234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>275233; 303178</t>
+          <t>274815; 302818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58305; 75290</t>
+          <t>57183; 72996</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>167</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>84538</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>114665</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124660</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54088</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>80182</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>102632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>116316</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>32099</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84538</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>114665</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>124660</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55898</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>87991</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69435; 90770</t>
+          <t>74638; 95832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91714; 112468</t>
+          <t>103630; 126163</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105418; 125956</t>
+          <t>114325; 133716</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25719; 38126</t>
+          <t>45481; 60240</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73686; 96092</t>
+          <t>69564; 91538</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102841; 124719</t>
+          <t>91187; 112907</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>113071; 134526</t>
+          <t>105053; 126260</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47271; 62450</t>
+          <t>27241; 40293</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>148763; 180025</t>
+          <t>150429; 180375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202892; 231585</t>
+          <t>202724; 230765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>226690; 254778</t>
+          <t>225823; 255417</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>77650; 97697</t>
+          <t>77568; 97940</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>373402</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>530759</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>373402</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>530759</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>336981; 378576</t>
+          <t>351905; 393254</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>486435; 527029</t>
+          <t>511646; 548841</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>507772; 543676</t>
+          <t>563535; 600903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93844; 111272</t>
+          <t>126085; 145254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>350621; 394190</t>
+          <t>339361; 379085</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>511119; 550397</t>
+          <t>485730; 525483</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>562734; 600860</t>
+          <t>507027; 543833</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>134765; 157301</t>
+          <t>89886; 107975</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>702468; 762083</t>
+          <t>702365; 760534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1007259; 1064264</t>
+          <t>1006721; 1064836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1082965; 1135614</t>
+          <t>1082220; 1134290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>236071; 263118</t>
+          <t>221415; 248795</t>
         </is>
       </c>
     </row>
